--- a/JsonConverter/ExcelFiles/PlayerData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerData.xlsx
@@ -61,13 +61,13 @@
     <t>BaseDefense</t>
   </si>
   <si>
-    <t>BaseCritRate</t>
-  </si>
-  <si>
-    <t>BaseNormalSkillHaste</t>
-  </si>
-  <si>
-    <t>BaseSpecialSkillHaste</t>
+    <t>BaseCriticalRate</t>
+  </si>
+  <si>
+    <t>BaseBasicAttackHaste</t>
+  </si>
+  <si>
+    <t>BaseActiveSkillHaste</t>
   </si>
   <si>
     <t>NormalSkillId</t>
@@ -86,7 +86,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -109,6 +109,11 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Carlito"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -151,15 +156,21 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
@@ -172,6 +183,9 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -417,7 +431,7 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
@@ -428,89 +442,89 @@
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="7">
         <v>1000.0</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="7">
         <v>100.0</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="7">
         <v>50.0</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="8">
         <v>10.0</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="9">
         <v>0.0</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="8">
         <v>0.0</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="6" t="s">
         <v>22</v>
       </c>
     </row>

--- a/JsonConverter/ExcelFiles/PlayerData.xlsx
+++ b/JsonConverter/ExcelFiles/PlayerData.xlsx
@@ -61,13 +61,13 @@
     <t>BaseDefense</t>
   </si>
   <si>
-    <t>BaseCriticalRate</t>
-  </si>
-  <si>
-    <t>BaseBasicAttackHaste</t>
-  </si>
-  <si>
-    <t>BaseActiveSkillHaste</t>
+    <t>BaseCriticalChance</t>
+  </si>
+  <si>
+    <t>BasicAttackHaste</t>
+  </si>
+  <si>
+    <t>SignatureSkillHaste</t>
   </si>
   <si>
     <t>NormalSkillId</t>
@@ -79,14 +79,14 @@
     <t>용사</t>
   </si>
   <si>
-    <t>player_skill_normal_001</t>
+    <t>skill_player_001_basic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -106,6 +106,12 @@
       <name val="Carlito"/>
     </font>
     <font>
+      <b/>
+      <sz val="11.0"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Carlito"/>
@@ -116,7 +122,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,8 +141,14 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -150,6 +162,20 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
     </border>
   </borders>
@@ -169,22 +195,22 @@
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="2" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -516,7 +542,7 @@
         <v>50.0</v>
       </c>
       <c r="F4" s="8">
-        <v>10.0</v>
+        <v>0.1</v>
       </c>
       <c r="G4" s="9">
         <v>0.0</v>
@@ -524,7 +550,7 @@
       <c r="H4" s="8">
         <v>0.0</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="5" t="s">
         <v>22</v>
       </c>
     </row>
